--- a/DesignData/Original_Map.xlsx
+++ b/DesignData/Original_Map.xlsx
@@ -163,7 +163,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>height_half_extent</t>
+    <t>depth_half_extent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>

--- a/DesignData/Original_Map.xlsx
+++ b/DesignData/Original_Map.xlsx
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
   <si>
     <t>BOTH</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -242,6 +242,10 @@
   </si>
   <si>
     <t>map_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portal_radius</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -624,13 +628,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="10" max="10" width="13.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -670,8 +674,11 @@
       <c r="M1" t="s">
         <v>24</v>
       </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -711,8 +718,11 @@
       <c r="M2" t="s">
         <v>9</v>
       </c>
+      <c r="N2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10</v>
       </c>
@@ -746,8 +756,11 @@
       <c r="K3" t="s">
         <v>19</v>
       </c>
+      <c r="N3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>20</v>
       </c>
@@ -784,8 +797,11 @@
       <c r="M4">
         <v>10</v>
       </c>
+      <c r="N4">
+        <v>500</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>30</v>
       </c>
@@ -822,8 +838,11 @@
       <c r="M5">
         <v>10</v>
       </c>
+      <c r="N5">
+        <v>500</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>40</v>
       </c>
@@ -859,6 +878,9 @@
       </c>
       <c r="M6">
         <v>10</v>
+      </c>
+      <c r="N6">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
